--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoTheta_3EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoTheta_3EM_MT_S3.xlsx
@@ -389,7 +389,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>318.869173741481</v>
+        <v>315.778215561405</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>52.7969525144744</v>
+        <v>54.5375734988211</v>
       </c>
     </row>
     <row r="4">
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>16.5575592946087</v>
+        <v>17.2708473261405</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>241.664359306649</v>
+        <v>239.11898366122</v>
       </c>
     </row>
     <row r="6">
@@ -421,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>274.837885882644</v>
+        <v>270.532420912034</v>
       </c>
     </row>
     <row r="7">
@@ -429,7 +429,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>305.433504289296</v>
+        <v>301.022443513133</v>
       </c>
     </row>
     <row r="8">
@@ -437,7 +437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>363.35320101411</v>
+        <v>361.872403093533</v>
       </c>
     </row>
     <row r="9">
@@ -445,7 +445,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>477.368267516277</v>
+        <v>479.654853956694</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>0.561997693029829</v>
+        <v>0.610266972484722</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2.25413032418369</v>
+        <v>2.28630375214477</v>
       </c>
     </row>
   </sheetData>

--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoTheta_3EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/ResumoTheta_3EM_MT_S3.xlsx
@@ -389,7 +389,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>315.778215561405</v>
+        <v>317.689663332277</v>
       </c>
     </row>
     <row r="3">
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>54.5375734988211</v>
+        <v>52.7558926365069</v>
       </c>
     </row>
     <row r="4">
@@ -405,7 +405,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>17.2708473261405</v>
+        <v>16.606109271276</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>239.11898366122</v>
+        <v>241.797879187085</v>
       </c>
     </row>
     <row r="6">
@@ -421,7 +421,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>270.532420912034</v>
+        <v>273.906138850624</v>
       </c>
     </row>
     <row r="7">
@@ -429,7 +429,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>301.022443513133</v>
+        <v>303.728253896732</v>
       </c>
     </row>
     <row r="8">
@@ -437,7 +437,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>361.872403093533</v>
+        <v>362.440538384358</v>
       </c>
     </row>
     <row r="9">
@@ -445,7 +445,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>479.654853956694</v>
+        <v>476.134785707996</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>0.610266972484722</v>
+        <v>0.574371603459302</v>
       </c>
     </row>
     <row r="11">
@@ -461,7 +461,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2.28630375214477</v>
+        <v>2.24514019437578</v>
       </c>
     </row>
   </sheetData>
